--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.79951538625775</v>
+        <v>2.079921250266884</v>
       </c>
       <c r="D2" t="n">
-        <v>19.74279052661447</v>
+        <v>3.208203460574851</v>
       </c>
       <c r="E2" t="n">
-        <v>19.24650652512098</v>
+        <v>3.127557310332159</v>
       </c>
       <c r="F2" t="n">
-        <v>12.68279345391946</v>
+        <v>2.060953936261913</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.73452837754188</v>
+        <v>3.694360861350556</v>
       </c>
       <c r="D3" t="n">
-        <v>11.10650710169493</v>
+        <v>1.804807404025426</v>
       </c>
       <c r="E3" t="n">
-        <v>19.24650652512098</v>
+        <v>3.127557310332159</v>
       </c>
       <c r="F3" t="n">
-        <v>12.68279345391946</v>
+        <v>2.060953936261913</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.981466554560578</v>
+        <v>0.971988315116094</v>
       </c>
       <c r="D4" t="n">
-        <v>4.251877913488439</v>
+        <v>0.6909301609418713</v>
       </c>
       <c r="E4" t="n">
-        <v>19.24650652512098</v>
+        <v>3.127557310332159</v>
       </c>
       <c r="F4" t="n">
-        <v>12.68279345391946</v>
+        <v>2.060953936261913</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.36409675690254</v>
+        <v>4.934165722996664</v>
       </c>
       <c r="D5" t="n">
-        <v>33.08689155882696</v>
+        <v>5.376619878309381</v>
       </c>
       <c r="E5" t="n">
-        <v>19.24650652512098</v>
+        <v>3.127557310332159</v>
       </c>
       <c r="F5" t="n">
-        <v>12.68279345391946</v>
+        <v>2.060953936261913</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.79391018606182</v>
+        <v>6.954010405235045</v>
       </c>
       <c r="D6" t="n">
-        <v>19.40580247968695</v>
+        <v>3.15344290294913</v>
       </c>
       <c r="E6" t="n">
-        <v>19.24650652512098</v>
+        <v>3.127557310332159</v>
       </c>
       <c r="F6" t="n">
-        <v>12.68279345391946</v>
+        <v>2.060953936261913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.67008986341722</v>
+        <v>10.3463896028053</v>
       </c>
       <c r="D7" t="n">
-        <v>41.94298460719519</v>
+        <v>6.815734998669218</v>
       </c>
       <c r="E7" t="n">
-        <v>19.24650652512098</v>
+        <v>3.127557310332159</v>
       </c>
       <c r="F7" t="n">
-        <v>12.68279345391946</v>
+        <v>2.060953936261913</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
